--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect – R01561308</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ab075046d2a5df</t>
+          <t>https://www.indeed.com/viewjob?jk=d3fc7cad7b621a95</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect – R01561308</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ab075046d2a5df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Full Stack AI Engineer (Senior Software Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8915b5aa273f1b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,54 +741,54 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Keystone</t>
+          <t>Dir, AI Platform Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>NYC Health + Hospitals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a103161b01705039</t>
+          <t>https://www.indeed.com/viewjob?jk=34c920d00f0a63af</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack AI Engineer (Senior Software Engineer)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8915b5aa273f1b5b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Sr. Software Engineer- Keystone</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a103161b01705039</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Managing Architect - Solution Architecture</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hilliard, FL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Managing Architect - Solution Architecture</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>SAP FICO Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Hilliard, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,40 +2351,775 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cargomatic</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IvoryCloud</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Match Made Tech</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Datavant</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Filevine</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Merz Aesthetics</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Racine, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Databricks engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Engineer - Amazon Connect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Oncourse Home Solutions</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hyundai Capital America</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hyundai Capital America</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>R&amp;T Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Safran Cabin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Teradata Developer-3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Radiant Digital</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>American business solutions inc</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D77" t="n">
         <v>10.4</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Managing Architect - Solution Architecture</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant</t>
+          <t>Managing Architect - Solution Architecture</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hilliard, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
+          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>SAP FICO Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hilliard, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R&amp;T Software Engineer 3</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Safran Cabin</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>R&amp;T Software Engineer 3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Safran Cabin</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3116,10 +3116,80 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,52 +2341,52 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,120 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Radiant Digital</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dir, AI Platform Engineering</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYC Health + Hospitals</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c920d00f0a63af</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Dir, AI Platform Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>NYC Health + Hospitals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=34c920d00f0a63af</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Full Stack AI Engineer (Senior Software Engineer)</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8915b5aa273f1b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java Full Stack AI Engineer (Senior Software Engineer)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8915b5aa273f1b5b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Keystone</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a103161b01705039</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr. Software Engineer- Keystone</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a103161b01705039</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Managing Architect - Solution Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hilliard, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Managing Architect - Solution Architecture</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SAP FICO Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hilliard, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R&amp;T Software Engineer 3</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Safran Cabin</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,29 +3041,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>R&amp;T Software Engineer 3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Safran Cabin</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
+          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3291,10 +3291,80 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e014fe941f1f22ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=31ba26cff0eff16a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=dce2730f22d939ec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Managing Architect - Solution Architecture</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hilliard, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
+          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer New</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer New</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Managing Architect - Solution Architecture</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>SAP FICO Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Hilliard, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,77 +2446,77 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,46 +2652,46 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Enterprise Azure Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>ValueBase Consulting</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Trumbull, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=bfbd690b76118449</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hyundai Capital America</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R&amp;T Software Engineer 3</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Safran Cabin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Hyundai Capital America</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,15 +3356,330 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hyundai Capital America</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R&amp;T Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Safran Cabin</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Teradata Developer-3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Radiant Digital</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect – R01561308</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ab075046d2a5df</t>
+          <t>https://www.indeed.com/viewjob?jk=595c67b5e42359ba</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dir, AI Platform Engineering</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NYC Health + Hospitals</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c920d00f0a63af</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Full Stack AI Engineer (Senior Software Engineer)</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8915b5aa273f1b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,46 +1182,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Keystone</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a103161b01705039</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GenAI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e014fe941f1f22ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ba26cff0eff16a</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce2730f22d939ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glue, Redshift, RDS, Azure, Data Factory, Snowflake, Oracle, SQL Server, PostgreSQL, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1594a1814d7cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02303f42368166</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer New</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer New</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Managing Architect - Solution Architecture</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ae70f3036cdeed</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hilliard, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,207 +2246,207 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Azure Data Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ValueBase Consulting</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Trumbull, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbd690b76118449</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,54 +3016,54 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3072,11 +3072,11 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,602 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Databricks engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Engineer - Amazon Connect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Oncourse Home Solutions</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Naperville, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Azure Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>IQZ SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>California State Personnel Board</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, SQL Server, PostgreSQL, NoSQL, AKS</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25313f83b8938e18</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2083fa3bb22ffe9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hyundai Capital America</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5160c34d455c60</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Hyundai Capital America</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78a9bc593b0f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>R&amp;T Software Engineer 3</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Safran Cabin</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Data Modeling, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d390689f78ce46c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Ethos Veterinary Health</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Miller Cooper</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Teradata Developer-3</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Radiant Digital</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>American business solutions inc</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,139 +2201,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,155 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Radiant Digital</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,69 +2306,69 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,42 +2806,42 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595c67b5e42359ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Sr. Report Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>JIG-SAW US, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Fullstack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Stash</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Scala, Kafka, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=826bc977d2b8d6c3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,35 +713,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Scala, Snowflake, Oracle</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Sixth Street</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stash</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Scala, Kafka, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826bc977d2b8d6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,225 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Teradata Developer-3</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Priority Dispatch Corp.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,94 +2421,94 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Platform (Frameworks, AI, Automation) Sr. Associate New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sixth Street</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,172 +3051,172 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0529d8ff520672</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,29 +3321,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,225 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12c78d6e39fc674e</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Teradata Developer-3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Sr. Report Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Report Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, dbt, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16a49ed3afacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priority Dispatch Corp.</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961b8ef9a31220a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,69 +2481,69 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,29 +3321,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c78d6e39fc674e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>NetSPI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,77 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Report Developer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Report Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,77 +1151,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI/ML-powered IoT Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JIG-SAW US, Inc.</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Hive, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f03868858d07644</t>
+          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,29 +3321,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer (Golang/Platform)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NetSPI</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=830d0bff9058d600</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NetSPI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Report Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Sr. Report Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,77 +1431,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,199 +2526,199 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,147 +3251,147 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Golang/Platform)</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=830d0bff9058d600</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NetSPI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Backend Engineer (Golang/Platform)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=830d0bff9058d600</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NetSPI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,15 +3741,260 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Teradata Developer-3</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Databricks Developer-3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trust Technology Solutions</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,52 +1396,52 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t xml:space="preserve">Tailored Edge Connections </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>North Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=17621e07d085bab3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Rogers, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,59 +3436,59 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, SQL Server, ETL, ELT, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45ca07d46e3db0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,29 +3601,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer, Associate - Physical Security</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NetSPI</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Data Modeling, Tableau, Splunk, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
+          <t>https://www.indeed.com/viewjob?jk=5038d894bf6c5b04</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,52 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NetSPI</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Report Developer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f10d62f4eab770e</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tailored Edge Connections </t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Aurora, IL, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17621e07d085bab3</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Architect, Service &amp; Operational Data</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer (Selenium/Java) – On-site (The Woodlands, TX)</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b69a3711f0d9d53</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,94 +1931,94 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Software Engineer - .NET, AWS (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=49d97f5a04a74b2d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,382 +2386,382 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rogers, AR, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Network Engineer / Architect (Cloud &amp; Private Cloud)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44bf9d7c469c1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=695b20750ce3efc8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Network Engineer / Architect (Cloud &amp; Private Cloud)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd76f4dc673f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=79844f5abf0ab0c8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Miller Cooper</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Ethos Veterinary Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Teradata Developer-3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Platform Engineer, Associate - Physical Security</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Data Modeling, Tableau, Splunk, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,427 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Golang/Platform)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Bird Rides</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=830d0bff9058d600</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Platform Engineer, Associate - Physical Security</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Blackstone</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Data Modeling, Tableau, Splunk, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5038d894bf6c5b04</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Cassandra, NoSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22183246282dc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Miller Cooper</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Ethos Veterinary Health</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Softnice</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>North Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Teradata Developer-3</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NetSPI</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c43e0c9ccd4fc4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-24.xlsx
+++ b/results/job_matches_2026-02-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Quality Engineer I (37_2026.1)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>27.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3fc7cad7b621a95</t>
+          <t>https://www.indeed.com/viewjob?jk=c7933ce6e87f7544</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
+          <t>https://www.indeed.com/viewjob?jk=d3fc7cad7b621a95</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
+          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
+          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8a49e90b17f1b9</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
+          <t>https://www.indeed.com/viewjob?jk=59ad45087f0478af</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
+          <t>https://www.indeed.com/viewjob?jk=006cef078e473c76</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce84cfffa53abdae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffea329c9e632fe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=07cde8b42f3da231</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ML Ops</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b77832b864a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9fbf9321e91c82</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Austin, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer - ML Ops</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mulligan Funding, LLC</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,49 +1406,49 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
+          <t>https://www.indeed.com/viewjob?jk=7db54c6b588d8f5c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,77 +1581,77 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Mulligan Funding, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Polars, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=b83efe663e7f5074</t>
         </is>
       </c>
     </row>
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=d9295dd5dd4ae3b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - .NET, AWS (Remote)</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d97f5a04a74b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac51481516fb7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vontier</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>(1357) Senior Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>HOPE MEDIA GROUP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
+          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Vontier</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, SQL Server, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa27cef936c5867</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - .NET, AWS (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=49d97f5a04a74b2d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=958f0954c73ffb6c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Network Engineer / Architect (Cloud &amp; Private Cloud)</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695b20750ce3efc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Network Engineer / Architect (Cloud &amp; Private Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79844f5abf0ab0c8</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, PostgreSQL, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a200fed649475457</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Databricks engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ethos Veterinary Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Teradata Developer-3</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7879b97287c803</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer, Associate - Physical Security</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,15 +3601,330 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Konrad Group</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ethos Veterinary Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f06c70b6fcc766c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Platform Engineer, Associate - Physical Security</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Blackstone</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Scala, Kafka, Data Modeling, Tableau, Splunk, Git</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5038d894bf6c5b04</t>
         </is>
